--- a/sheets/조재수대금교본/검수/청성곡.xlsx
+++ b/sheets/조재수대금교본/검수/청성곡.xlsx
@@ -2573,16 +2573,15 @@
       <c r="B4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林南
-ﾉ
 林
-–太∽</t>
+–太</t>
         </is>
       </c>
       <c r="C4" s="22"/>
       <c r="D4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">∽汰潢
-汰∧
+          <t xml:space="preserve">汰潢
+汰
 –</t>
         </is>
       </c>
@@ -2592,8 +2591,7 @@
       <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–∼
-ИИ</t>
+–∼</t>
         </is>
       </c>
       <c r="I4" s="22"/>
@@ -2609,14 +2607,14 @@
         <is>
           <t xml:space="preserve">潢∼
 –
-∧汰㳞</t>
+汰㳞</t>
         </is>
       </c>
       <c r="M4" s="22"/>
       <c r="N4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-太ㄷ∽
+太
 –</t>
         </is>
       </c>
@@ -2628,8 +2626,7 @@
         <is>
           <t xml:space="preserve">林
 –∼
-林∧
-‹</t>
+林</t>
         </is>
       </c>
       <c r="C5" s="22"/>
@@ -2645,15 +2642,15 @@
         <is>
           <t xml:space="preserve">仲
 –
-–ﾉ</t>
+–</t>
         </is>
       </c>
       <c r="I5" s="22"/>
       <c r="J5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢ʒ
+          <t xml:space="preserve">潢
 㳞
-汰ʒ∽</t>
+汰</t>
         </is>
       </c>
       <c r="K5" s="22"/>
@@ -2666,17 +2663,17 @@
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林ㄷ
+          <t xml:space="preserve">林
 –∼
-–И</t>
+–</t>
         </is>
       </c>
       <c r="C6" s="22"/>
       <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–汰∧
-–⌝</t>
+–汰
+–</t>
         </is>
       </c>
       <c r="E6" s="22"/>
@@ -2684,9 +2681,9 @@
       <c r="G6" s="22"/>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太ʒ黃
+          <t xml:space="preserve">太黃
 –∼
-–И</t>
+–</t>
         </is>
       </c>
       <c r="I6" s="22"/>
@@ -2694,7 +2691,7 @@
         <is>
           <t xml:space="preserve">潢
 △
-∽汰潢</t>
+汰潢</t>
         </is>
       </c>
       <c r="K6" s="22"/>
@@ -2713,9 +2710,8 @@
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林ㄷ
+          <t xml:space="preserve">林
 南
-ﾉ
 △</t>
         </is>
       </c>
@@ -2724,7 +2720,7 @@
         <is>
           <t xml:space="preserve">林∼
 –
-–ㄴ</t>
+–</t>
         </is>
       </c>
       <c r="E7" s="22"/>
@@ -2734,7 +2730,7 @@
         <is>
           <t xml:space="preserve">仲·
 △
-仲太ㄷ</t>
+仲太</t>
         </is>
       </c>
       <c r="I7" s="22"/>
@@ -2750,7 +2746,7 @@
       <c r="M7" s="22"/>
       <c r="N7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林ㄷ</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="O7" s="22"/>
@@ -2761,14 +2757,14 @@
         <is>
           <t xml:space="preserve">潢∼
 –
-∧汰㳞</t>
+汰㳞</t>
         </is>
       </c>
       <c r="C8" s="22"/>
       <c r="D8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢ʒ㳞
-汰ʒ潢
+          <t xml:space="preserve">潢㳞
+汰潢
 △</t>
         </is>
       </c>
@@ -2788,7 +2784,7 @@
       <c r="L8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰潢㳞
-汰∽
+汰
 –</t>
         </is>
       </c>
@@ -2797,7 +2793,7 @@
         <is>
           <t xml:space="preserve">–
 –∼
-潢南林∽</t>
+潢南林</t>
         </is>
       </c>
       <c r="O8" s="22"/>
@@ -2808,7 +2804,7 @@
       <c r="C9" s="22"/>
       <c r="D9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">∽汰潢
+          <t xml:space="preserve">汰潢
 –
 –</t>
         </is>
@@ -2826,8 +2822,7 @@
         <is>
           <t xml:space="preserve">南
 –
-–ﾉ
-‹</t>
+–</t>
         </is>
       </c>
       <c r="K9" s="22"/>
@@ -2837,7 +2832,7 @@
         <is>
           <t xml:space="preserve">潢·
 △
-∽汰潢</t>
+汰潢</t>
         </is>
       </c>
       <c r="O9" s="22"/>
@@ -2863,14 +2858,14 @@
       <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–太∧
+–太
 黃△</t>
         </is>
       </c>
       <c r="I10" s="22"/>
       <c r="J10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林ㄷ</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="K10" s="22"/>
@@ -2895,8 +2890,8 @@
       <c r="C11" s="22"/>
       <c r="D11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢ʒ㳞
-汰∽
+          <t xml:space="preserve">潢㳞
+汰
 –</t>
         </is>
       </c>
@@ -2908,14 +2903,13 @@
       <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–
-И</t>
+–</t>
         </is>
       </c>
       <c r="K11" s="22"/>
       <c r="L11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">И潢
+          <t xml:space="preserve">潢
 △
 –</t>
         </is>
@@ -2925,7 +2919,7 @@
         <is>
           <t xml:space="preserve">–∼
 –㳞
-∽汰潢</t>
+汰潢</t>
         </is>
       </c>
       <c r="O11" s="22"/>
@@ -2935,7 +2929,7 @@
       <c r="B12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰潢㳞
-汰∽
+汰
 –</t>
         </is>
       </c>
@@ -2943,7 +2937,7 @@
       <c r="D12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–∼
-∧汰И
+汰
 潢△</t>
         </is>
       </c>
@@ -2960,17 +2954,17 @@
       <c r="K12" s="22"/>
       <c r="L12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">ʒ潢㳞
-汰∽
+          <t xml:space="preserve">潢㳞
+汰
 –</t>
         </is>
       </c>
       <c r="M12" s="22"/>
       <c r="N12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林ㄷ
+          <t xml:space="preserve">林
 △
-林ㄷ</t>
+林</t>
         </is>
       </c>
       <c r="O12" s="22"/>
@@ -2981,7 +2975,7 @@
       <c r="C13" s="22"/>
       <c r="D13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">∽汰潢
+          <t xml:space="preserve">汰潢
 –
 –</t>
         </is>
@@ -2995,7 +2989,7 @@
         <is>
           <t xml:space="preserve">–
 –㳞
-∽汰潢</t>
+汰潢</t>
         </is>
       </c>
       <c r="K13" s="22"/>
@@ -3032,7 +3026,7 @@
       <c r="I14" s="22"/>
       <c r="J14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林ㄷ
+          <t xml:space="preserve">林
 △
 林</t>
         </is>
@@ -3050,8 +3044,7 @@
         <is>
           <t xml:space="preserve">仲
 –
-ﾉ
-太∽</t>
+太</t>
         </is>
       </c>
       <c r="O14" s="22"/>
@@ -3060,7 +3053,7 @@
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">И潢
+          <t xml:space="preserve">潢
 △
 –</t>
         </is>
@@ -3070,8 +3063,7 @@
         <is>
           <t xml:space="preserve">南
 –
-–ﾉ
-‹</t>
+–</t>
         </is>
       </c>
       <c r="E15" s="22"/>
@@ -3083,15 +3075,15 @@
       <c r="K15" s="22"/>
       <c r="L15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∧
-潢ʒ
+          <t xml:space="preserve">汰
+潢
 南林</t>
         </is>
       </c>
       <c r="M15" s="22"/>
       <c r="N15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林ㄷ∼
+          <t xml:space="preserve">林∼
 –
 南·</t>
         </is>

--- a/sheets/조재수대금교본/검수/청성곡.xlsx
+++ b/sheets/조재수대금교본/검수/청성곡.xlsx
@@ -2573,15 +2573,16 @@
       <c r="B4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林南
+ﾉ
 林
-–太</t>
+–太∽</t>
         </is>
       </c>
       <c r="C4" s="22"/>
       <c r="D4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰潢
-汰
+          <t xml:space="preserve">∽汰潢
+汰∧
 –</t>
         </is>
       </c>
@@ -2591,7 +2592,8 @@
       <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–∼</t>
+–∼
+ИИ</t>
         </is>
       </c>
       <c r="I4" s="22"/>
@@ -2607,14 +2609,14 @@
         <is>
           <t xml:space="preserve">潢∼
 –
-汰㳞</t>
+∧汰㳞</t>
         </is>
       </c>
       <c r="M4" s="22"/>
       <c r="N4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-太
+太ㄷ∽
 –</t>
         </is>
       </c>
@@ -2626,7 +2628,7 @@
         <is>
           <t xml:space="preserve">林
 –∼
-林</t>
+林∧</t>
         </is>
       </c>
       <c r="C5" s="22"/>
@@ -2642,15 +2644,15 @@
         <is>
           <t xml:space="preserve">仲
 –
-–</t>
+–ﾉ</t>
         </is>
       </c>
       <c r="I5" s="22"/>
       <c r="J5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
+          <t xml:space="preserve">潢ʒ
 㳞
-汰</t>
+汰ʒ∽</t>
         </is>
       </c>
       <c r="K5" s="22"/>
@@ -2663,17 +2665,17 @@
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
+          <t xml:space="preserve">林ㄷ
 –∼
-–</t>
+–И</t>
         </is>
       </c>
       <c r="C6" s="22"/>
       <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–汰
-–</t>
+–汰∧
+–⌝</t>
         </is>
       </c>
       <c r="E6" s="22"/>
@@ -2681,9 +2683,9 @@
       <c r="G6" s="22"/>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太黃
+          <t xml:space="preserve">太ʒ黃
 –∼
-–</t>
+–И</t>
         </is>
       </c>
       <c r="I6" s="22"/>
@@ -2691,7 +2693,7 @@
         <is>
           <t xml:space="preserve">潢
 △
-汰潢</t>
+∽汰潢</t>
         </is>
       </c>
       <c r="K6" s="22"/>
@@ -2710,8 +2712,9 @@
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
+          <t xml:space="preserve">林ㄷ
 南
+ﾉ
 △</t>
         </is>
       </c>
@@ -2720,7 +2723,7 @@
         <is>
           <t xml:space="preserve">林∼
 –
-–</t>
+–ㄴ</t>
         </is>
       </c>
       <c r="E7" s="22"/>
@@ -2730,7 +2733,7 @@
         <is>
           <t xml:space="preserve">仲·
 △
-仲太</t>
+仲太ㄷ</t>
         </is>
       </c>
       <c r="I7" s="22"/>
@@ -2746,7 +2749,7 @@
       <c r="M7" s="22"/>
       <c r="N7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林</t>
+          <t xml:space="preserve">林ㄷ</t>
         </is>
       </c>
       <c r="O7" s="22"/>
@@ -2757,14 +2760,14 @@
         <is>
           <t xml:space="preserve">潢∼
 –
-汰㳞</t>
+∧汰㳞</t>
         </is>
       </c>
       <c r="C8" s="22"/>
       <c r="D8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢㳞
-汰潢
+          <t xml:space="preserve">潢ʒ㳞
+汰ʒ潢
 △</t>
         </is>
       </c>
@@ -2784,7 +2787,7 @@
       <c r="L8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰潢㳞
-汰
+汰∽
 –</t>
         </is>
       </c>
@@ -2793,7 +2796,7 @@
         <is>
           <t xml:space="preserve">–
 –∼
-潢南林</t>
+潢南林∽</t>
         </is>
       </c>
       <c r="O8" s="22"/>
@@ -2804,7 +2807,7 @@
       <c r="C9" s="22"/>
       <c r="D9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰潢
+          <t xml:space="preserve">∽汰潢
 –
 –</t>
         </is>
@@ -2822,7 +2825,7 @@
         <is>
           <t xml:space="preserve">南
 –
-–</t>
+–ﾉ</t>
         </is>
       </c>
       <c r="K9" s="22"/>
@@ -2832,7 +2835,7 @@
         <is>
           <t xml:space="preserve">潢·
 △
-汰潢</t>
+∽汰潢</t>
         </is>
       </c>
       <c r="O9" s="22"/>
@@ -2858,14 +2861,14 @@
       <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–太
+–太∧
 黃△</t>
         </is>
       </c>
       <c r="I10" s="22"/>
       <c r="J10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林</t>
+          <t xml:space="preserve">林ㄷ</t>
         </is>
       </c>
       <c r="K10" s="22"/>
@@ -2890,8 +2893,8 @@
       <c r="C11" s="22"/>
       <c r="D11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢㳞
-汰
+          <t xml:space="preserve">潢ʒ㳞
+汰∽
 –</t>
         </is>
       </c>
@@ -2903,13 +2906,14 @@
       <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–</t>
+–
+И</t>
         </is>
       </c>
       <c r="K11" s="22"/>
       <c r="L11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
+          <t xml:space="preserve">И潢
 △
 –</t>
         </is>
@@ -2919,7 +2923,7 @@
         <is>
           <t xml:space="preserve">–∼
 –㳞
-汰潢</t>
+∽汰潢</t>
         </is>
       </c>
       <c r="O11" s="22"/>
@@ -2929,7 +2933,7 @@
       <c r="B12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰潢㳞
-汰
+汰∽
 –</t>
         </is>
       </c>
@@ -2937,7 +2941,7 @@
       <c r="D12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–∼
-汰
+∧汰И
 潢△</t>
         </is>
       </c>
@@ -2954,17 +2958,17 @@
       <c r="K12" s="22"/>
       <c r="L12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢㳞
-汰
+          <t xml:space="preserve">ʒ潢㳞
+汰∽
 –</t>
         </is>
       </c>
       <c r="M12" s="22"/>
       <c r="N12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
+          <t xml:space="preserve">林ㄷ
 △
-林</t>
+林ㄷ</t>
         </is>
       </c>
       <c r="O12" s="22"/>
@@ -2975,7 +2979,7 @@
       <c r="C13" s="22"/>
       <c r="D13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰潢
+          <t xml:space="preserve">∽汰潢
 –
 –</t>
         </is>
@@ -2989,7 +2993,7 @@
         <is>
           <t xml:space="preserve">–
 –㳞
-汰潢</t>
+∽汰潢</t>
         </is>
       </c>
       <c r="K13" s="22"/>
@@ -3026,7 +3030,7 @@
       <c r="I14" s="22"/>
       <c r="J14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
+          <t xml:space="preserve">林ㄷ
 △
 林</t>
         </is>
@@ -3044,7 +3048,8 @@
         <is>
           <t xml:space="preserve">仲
 –
-太</t>
+ﾉ
+太∽</t>
         </is>
       </c>
       <c r="O14" s="22"/>
@@ -3053,7 +3058,7 @@
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
+          <t xml:space="preserve">И潢
 △
 –</t>
         </is>
@@ -3063,7 +3068,7 @@
         <is>
           <t xml:space="preserve">南
 –
-–</t>
+–ﾉ</t>
         </is>
       </c>
       <c r="E15" s="22"/>
@@ -3075,15 +3080,15 @@
       <c r="K15" s="22"/>
       <c r="L15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-潢
+          <t xml:space="preserve">汰∧
+潢ʒ
 南林</t>
         </is>
       </c>
       <c r="M15" s="22"/>
       <c r="N15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林∼
+          <t xml:space="preserve">林ㄷ∼
 –
 南·</t>
         </is>

--- a/sheets/조재수대금교본/검수/청성곡.xlsx
+++ b/sheets/조재수대금교본/검수/청성곡.xlsx
@@ -2511,26 +2511,26 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="18.03" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="18.03" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="18.03" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="18.03" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="18.03" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="18.03" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="18.03" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="121.21" customHeight="true">
+    <row r="2" ht="93.02" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
       <c r="N2" s="20"/>
       <c r="O2" s="20"/>
     </row>
-    <row r="3" ht="155.06" customHeight="true">
+    <row r="3" ht="118.9" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21"/>
       <c r="C3" s="22"/>
@@ -2568,7 +2568,7 @@
       <c r="N3" s="21"/>
       <c r="O3" s="22"/>
     </row>
-    <row r="4" ht="155.06" customHeight="true">
+    <row r="4" ht="118.9" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="O4" s="22"/>
     </row>
-    <row r="5" ht="155.06" customHeight="true">
+    <row r="5" ht="118.9" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
       <c r="N5" s="21"/>
       <c r="O5" s="22"/>
     </row>
-    <row r="6" ht="155.06" customHeight="true">
+    <row r="6" ht="118.9" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
       <c r="N6" s="21"/>
       <c r="O6" s="22"/>
     </row>
-    <row r="7" ht="155.06" customHeight="true">
+    <row r="7" ht="118.9" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="O7" s="22"/>
     </row>
-    <row r="8" ht="155.06" customHeight="true">
+    <row r="8" ht="118.9" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="O8" s="22"/>
     </row>
-    <row r="9" ht="155.06" customHeight="true">
+    <row r="9" ht="118.9" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21"/>
       <c r="C9" s="22"/>
@@ -2840,7 +2840,7 @@
       </c>
       <c r="O9" s="22"/>
     </row>
-    <row r="10" ht="155.06" customHeight="true">
+    <row r="10" ht="118.9" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -2881,7 +2881,7 @@
       <c r="N10" s="21"/>
       <c r="O10" s="22"/>
     </row>
-    <row r="11" ht="155.06" customHeight="true">
+    <row r="11" ht="118.9" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="O11" s="22"/>
     </row>
-    <row r="12" ht="155.06" customHeight="true">
+    <row r="12" ht="118.9" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="O12" s="22"/>
     </row>
-    <row r="13" ht="155.06" customHeight="true">
+    <row r="13" ht="118.9" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="22"/>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="O13" s="22"/>
     </row>
-    <row r="14" ht="155.06" customHeight="true">
+    <row r="14" ht="118.9" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="O14" s="22"/>
     </row>
-    <row r="15" ht="155.06" customHeight="true">
+    <row r="15" ht="118.9" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
       </c>
       <c r="O15" s="22"/>
     </row>
-    <row r="16" ht="155.06" customHeight="true">
+    <row r="16" ht="118.9" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
       <c r="C16" s="22"/>
@@ -3118,6 +3118,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="33"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="43"/>
 </worksheet>
 </file>